--- a/PULSERAS SWA.xlsx
+++ b/PULSERAS SWA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E1B252-C31C-4C3C-853E-FF2D777E7190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C572C3-7BBE-49A9-A2E2-4F4AD40EF82A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC752115-4679-4725-9595-0BAF90178FFC}"/>
   </bookViews>
@@ -120,7 +120,7 @@
     <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="166" formatCode="_-[$Q-100A]* #,##0.00_-;\-[$Q-100A]* #,##0.00_-;_-[$Q-100A]* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,6 +157,14 @@
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -245,10 +253,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -283,8 +292,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -306,13 +319,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>295275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1362075</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>981075</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -349,13 +362,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>295275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1343025</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>1028700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -392,13 +405,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1343025</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>1009650</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -435,13 +448,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>333375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1304925</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>1057275</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -478,13 +491,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>323850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>904875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -521,13 +534,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>361950</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1295400</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>923925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -559,6 +572,50 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>266701</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1285875</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>909211</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Imagen 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AECAA509-262C-F711-5505-786DD1070A31}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1609725" y="942976"/>
+          <a:ext cx="1152525" cy="642510"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
@@ -883,7 +940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D45025-46D8-4DF0-A314-E30E9C4D1102}">
-  <dimension ref="A2:L547"/>
+  <dimension ref="A2:L548"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -954,55 +1011,36 @@
     </row>
     <row r="4" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>6</v>
+        <v>142</v>
       </c>
       <c r="B4" s="3">
         <v>15</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="5">
-        <v>5.14</v>
-      </c>
-      <c r="E4" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F4" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G4" s="8">
-        <f>D4+E4+F4</f>
-        <v>6.03</v>
-      </c>
-      <c r="H4" s="7">
-        <f>G4*8</f>
-        <v>48.24</v>
-      </c>
-      <c r="I4" s="7">
-        <f>H4/0.95</f>
-        <v>50.778947368421058</v>
-      </c>
-      <c r="J4" s="7">
-        <f>(I4*2)+5</f>
-        <v>106.55789473684212</v>
-      </c>
-      <c r="K4" s="7">
-        <v>110</v>
-      </c>
+      <c r="D4" s="14">
+        <v>5.48</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
       <c r="L4" s="9">
-        <f>K4+10</f>
-        <v>120</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="3">
         <v>15</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="5">
-        <v>5.29</v>
+        <v>5.14</v>
       </c>
       <c r="E5" s="6">
         <v>0.7</v>
@@ -1011,162 +1049,162 @@
         <v>0.19</v>
       </c>
       <c r="G5" s="8">
-        <f>D5+E5+F5</f>
-        <v>6.1800000000000006</v>
+        <f t="shared" ref="G5:G10" si="0">D5+E5+F5</f>
+        <v>6.03</v>
       </c>
       <c r="H5" s="7">
-        <f>G5*8</f>
-        <v>49.440000000000005</v>
+        <f t="shared" ref="H4:H10" si="1">G5*8</f>
+        <v>48.24</v>
       </c>
       <c r="I5" s="7">
-        <f>H5/0.95</f>
-        <v>52.0421052631579</v>
+        <f t="shared" ref="I4:I10" si="2">H5/0.95</f>
+        <v>50.778947368421058</v>
       </c>
       <c r="J5" s="7">
-        <f>(I5*2)+5</f>
-        <v>109.0842105263158</v>
+        <f t="shared" ref="J4:J10" si="3">(I5*2)+5</f>
+        <v>106.55789473684212</v>
       </c>
       <c r="K5" s="7">
         <v>110</v>
       </c>
       <c r="L5" s="9">
-        <f>K5+10</f>
+        <f t="shared" ref="L4:L10" si="4">K5+10</f>
         <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="5">
-        <v>11.31</v>
+        <v>5.29</v>
       </c>
       <c r="E6" s="6">
-        <v>1.17</v>
+        <v>0.7</v>
       </c>
       <c r="F6" s="7">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="G6" s="8">
-        <f>D6+E6+F6</f>
-        <v>12.8</v>
+        <f t="shared" si="0"/>
+        <v>6.1800000000000006</v>
       </c>
       <c r="H6" s="7">
-        <f>G6*8</f>
-        <v>102.4</v>
+        <f t="shared" si="1"/>
+        <v>49.440000000000005</v>
       </c>
       <c r="I6" s="7">
-        <f>H6/0.95</f>
-        <v>107.78947368421053</v>
+        <f t="shared" si="2"/>
+        <v>52.0421052631579</v>
       </c>
       <c r="J6" s="7">
-        <f>(I6*2)+5</f>
-        <v>220.57894736842107</v>
+        <f t="shared" si="3"/>
+        <v>109.0842105263158</v>
       </c>
       <c r="K6" s="7">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="L6" s="9">
-        <f>K6+10</f>
-        <v>230</v>
+        <f t="shared" si="4"/>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="5">
-        <v>6.61</v>
+        <v>11.31</v>
       </c>
       <c r="E7" s="6">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
       <c r="F7" s="7">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="G7" s="8">
-        <f>D7+E7+F7</f>
-        <v>7.8</v>
+        <f t="shared" si="0"/>
+        <v>12.8</v>
       </c>
       <c r="H7" s="7">
-        <f>G7*8</f>
-        <v>62.4</v>
+        <f t="shared" si="1"/>
+        <v>102.4</v>
       </c>
       <c r="I7" s="7">
-        <f>H7/0.95</f>
-        <v>65.684210526315795</v>
+        <f t="shared" si="2"/>
+        <v>107.78947368421053</v>
       </c>
       <c r="J7" s="7">
-        <f>(I7*2)+5</f>
-        <v>136.36842105263159</v>
+        <f t="shared" si="3"/>
+        <v>220.57894736842107</v>
       </c>
       <c r="K7" s="7">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="L7" s="9">
-        <f>K7+10</f>
-        <v>150</v>
+        <f t="shared" si="4"/>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="5">
-        <v>8.23</v>
-      </c>
-      <c r="E8" s="10">
-        <v>1.4</v>
+        <v>6.61</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.93</v>
       </c>
       <c r="F8" s="7">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
       <c r="G8" s="8">
-        <f>D8+E8+F8</f>
-        <v>10.020000000000001</v>
+        <f t="shared" si="0"/>
+        <v>7.8</v>
       </c>
       <c r="H8" s="7">
-        <f>G8*8</f>
-        <v>80.160000000000011</v>
+        <f t="shared" si="1"/>
+        <v>62.4</v>
       </c>
       <c r="I8" s="7">
-        <f>H8/0.95</f>
-        <v>84.378947368421066</v>
+        <f t="shared" si="2"/>
+        <v>65.684210526315795</v>
       </c>
       <c r="J8" s="7">
-        <f>(I8*2)+5</f>
-        <v>173.75789473684213</v>
+        <f t="shared" si="3"/>
+        <v>136.36842105263159</v>
       </c>
       <c r="K8" s="7">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="L8" s="9">
-        <f>K8+10</f>
-        <v>185</v>
+        <f t="shared" si="4"/>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" s="3">
         <v>30</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="5">
-        <v>6.61</v>
+        <v>8.23</v>
       </c>
       <c r="E9" s="10">
         <v>1.4</v>
@@ -1175,30 +1213,70 @@
         <v>0.39</v>
       </c>
       <c r="G9" s="8">
-        <f>D9+E9+F9</f>
+        <f t="shared" si="0"/>
+        <v>10.020000000000001</v>
+      </c>
+      <c r="H9" s="7">
+        <f t="shared" si="1"/>
+        <v>80.160000000000011</v>
+      </c>
+      <c r="I9" s="7">
+        <f t="shared" si="2"/>
+        <v>84.378947368421066</v>
+      </c>
+      <c r="J9" s="7">
+        <f t="shared" si="3"/>
+        <v>173.75789473684213</v>
+      </c>
+      <c r="K9" s="7">
+        <v>175</v>
+      </c>
+      <c r="L9" s="9">
+        <f t="shared" si="4"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>1</v>
+      </c>
+      <c r="B10" s="3">
+        <v>30</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="5">
+        <v>6.61</v>
+      </c>
+      <c r="E10" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0.39</v>
+      </c>
+      <c r="G10" s="8">
+        <f t="shared" si="0"/>
         <v>8.4</v>
       </c>
-      <c r="H9" s="7">
-        <f>G9*8</f>
+      <c r="H10" s="7">
+        <f t="shared" si="1"/>
         <v>67.2</v>
       </c>
-      <c r="I9" s="7">
-        <f>H9/0.95</f>
+      <c r="I10" s="7">
+        <f t="shared" si="2"/>
         <v>70.736842105263165</v>
       </c>
-      <c r="J9" s="7">
-        <f>(I9*2)+5</f>
+      <c r="J10" s="7">
+        <f t="shared" si="3"/>
         <v>146.47368421052633</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K10" s="7">
         <v>150</v>
       </c>
-      <c r="L9" s="9">
-        <f>K9+10</f>
+      <c r="L10" s="9">
+        <f t="shared" si="4"/>
         <v>160</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1736,24 +1814,26 @@
     <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:L9">
-    <sortCondition descending="1" ref="A4:A9"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:L10">
+    <sortCondition descending="1" ref="A5:A10"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D9" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{158232D1-5A33-4F23-96FE-CBBD1062997F}"/>
-    <hyperlink ref="D8" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E4E5833E-4068-4B7C-B15B-8751DDC64332}"/>
-    <hyperlink ref="D7" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{617E7749-47A4-47BF-9B49-B7021524E0CD}"/>
-    <hyperlink ref="D6" r:id="rId4" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{373D7045-F276-4CA0-92CD-7DDFEEF88D44}"/>
-    <hyperlink ref="D5" r:id="rId5" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{72EFFD19-DCEF-424B-99B5-9CD2ABDFC16A}"/>
-    <hyperlink ref="D4" r:id="rId6" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{2BAC9E25-EE87-4D34-BF2C-E18DBF9252D5}"/>
+    <hyperlink ref="D10" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{158232D1-5A33-4F23-96FE-CBBD1062997F}"/>
+    <hyperlink ref="D9" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E4E5833E-4068-4B7C-B15B-8751DDC64332}"/>
+    <hyperlink ref="D8" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{617E7749-47A4-47BF-9B49-B7021524E0CD}"/>
+    <hyperlink ref="D7" r:id="rId4" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{373D7045-F276-4CA0-92CD-7DDFEEF88D44}"/>
+    <hyperlink ref="D6" r:id="rId5" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{72EFFD19-DCEF-424B-99B5-9CD2ABDFC16A}"/>
+    <hyperlink ref="D5" r:id="rId6" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{2BAC9E25-EE87-4D34-BF2C-E18DBF9252D5}"/>
+    <hyperlink ref="D4" r:id="rId7" display="https://detail.1688.com/offer/1002175660973.html" xr:uid="{8B5C1529-184D-4C9D-8502-E6BCED7B68FF}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId7"/>
-  <drawing r:id="rId8"/>
+  <pageSetup orientation="portrait" r:id="rId8"/>
+  <drawing r:id="rId9"/>
 </worksheet>
 </file>
--- a/PULSERAS SWA.xlsx
+++ b/PULSERAS SWA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C572C3-7BBE-49A9-A2E2-4F4AD40EF82A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8EB13E-470E-43C6-8F48-48A7073723B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC752115-4679-4725-9595-0BAF90178FFC}"/>
   </bookViews>
@@ -287,14 +287,14 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -319,13 +319,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>295275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1362075</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>981075</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -362,13 +362,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>295275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1343025</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>1028700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -405,13 +405,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1343025</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>1009650</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -448,13 +448,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>333375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1304925</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>1057275</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -491,13 +491,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>323850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>904875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -534,13 +534,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>361950</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1295400</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>923925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -609,6 +609,94 @@
         <a:xfrm>
           <a:off x="1609725" y="942976"/>
           <a:ext cx="1152525" cy="642510"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>247650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1323975</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>993337</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagen 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E85CA698-196E-4592-A235-FE030F8E2335}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1552575" y="2190750"/>
+          <a:ext cx="1247775" cy="745687"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1266825</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>984667</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Imagen 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{940BB3CB-D3C6-249C-3C62-8609869745C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1571625" y="2171700"/>
+          <a:ext cx="1171575" cy="756067"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -940,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D45025-46D8-4DF0-A314-E30E9C4D1102}">
-  <dimension ref="A2:L548"/>
+  <dimension ref="A2:L550"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -956,20 +1044,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="22.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="14"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1017,7 +1105,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="14">
+      <c r="D4" s="11">
         <v>5.48</v>
       </c>
       <c r="E4" s="6"/>
@@ -1033,252 +1121,294 @@
     </row>
     <row r="5" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3">
         <v>15</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="5">
-        <v>5.14</v>
-      </c>
-      <c r="E5" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F5" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G5" s="8">
-        <f t="shared" ref="G5:G10" si="0">D5+E5+F5</f>
-        <v>6.03</v>
-      </c>
-      <c r="H5" s="7">
-        <f t="shared" ref="H4:H10" si="1">G5*8</f>
-        <v>48.24</v>
-      </c>
-      <c r="I5" s="7">
-        <f t="shared" ref="I4:I10" si="2">H5/0.95</f>
-        <v>50.778947368421058</v>
-      </c>
-      <c r="J5" s="7">
-        <f t="shared" ref="J4:J10" si="3">(I5*2)+5</f>
-        <v>106.55789473684212</v>
-      </c>
-      <c r="K5" s="7">
-        <v>110</v>
-      </c>
+      <c r="D5" s="11">
+        <v>6.68</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
       <c r="L5" s="9">
-        <f t="shared" ref="L4:L10" si="4">K5+10</f>
-        <v>120</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" s="3">
         <v>15</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="5">
-        <v>5.29</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F6" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G6" s="8">
-        <f t="shared" si="0"/>
-        <v>6.1800000000000006</v>
-      </c>
-      <c r="H6" s="7">
-        <f t="shared" si="1"/>
-        <v>49.440000000000005</v>
-      </c>
-      <c r="I6" s="7">
-        <f t="shared" si="2"/>
-        <v>52.0421052631579</v>
-      </c>
-      <c r="J6" s="7">
-        <f t="shared" si="3"/>
-        <v>109.0842105263158</v>
-      </c>
-      <c r="K6" s="7">
-        <v>110</v>
-      </c>
+      <c r="D6" s="11">
+        <v>7.43</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
       <c r="L6" s="9">
-        <f t="shared" si="4"/>
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="5">
-        <v>11.31</v>
+        <v>5.14</v>
       </c>
       <c r="E7" s="6">
-        <v>1.17</v>
+        <v>0.7</v>
       </c>
       <c r="F7" s="7">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="G7" s="8">
-        <f t="shared" si="0"/>
-        <v>12.8</v>
+        <f t="shared" ref="G7:G12" si="0">D7+E7+F7</f>
+        <v>6.03</v>
       </c>
       <c r="H7" s="7">
-        <f t="shared" si="1"/>
-        <v>102.4</v>
+        <f t="shared" ref="H7:H12" si="1">G7*8</f>
+        <v>48.24</v>
       </c>
       <c r="I7" s="7">
-        <f t="shared" si="2"/>
-        <v>107.78947368421053</v>
+        <f t="shared" ref="I7:I12" si="2">H7/0.95</f>
+        <v>50.778947368421058</v>
       </c>
       <c r="J7" s="7">
-        <f t="shared" si="3"/>
-        <v>220.57894736842107</v>
+        <f t="shared" ref="J7:J12" si="3">(I7*2)+5</f>
+        <v>106.55789473684212</v>
       </c>
       <c r="K7" s="7">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="L7" s="9">
-        <f t="shared" si="4"/>
-        <v>230</v>
+        <f t="shared" ref="L7:L12" si="4">K7+10</f>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="5">
-        <v>6.61</v>
+        <v>5.29</v>
       </c>
       <c r="E8" s="6">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="F8" s="7">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="G8" s="8">
         <f t="shared" si="0"/>
-        <v>7.8</v>
+        <v>6.1800000000000006</v>
       </c>
       <c r="H8" s="7">
         <f t="shared" si="1"/>
-        <v>62.4</v>
+        <v>49.440000000000005</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" si="2"/>
-        <v>65.684210526315795</v>
+        <v>52.0421052631579</v>
       </c>
       <c r="J8" s="7">
         <f t="shared" si="3"/>
-        <v>136.36842105263159</v>
+        <v>109.0842105263158</v>
       </c>
       <c r="K8" s="7">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="L8" s="9">
         <f t="shared" si="4"/>
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B9" s="3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="5">
-        <v>8.23</v>
-      </c>
-      <c r="E9" s="10">
-        <v>1.4</v>
+        <v>11.31</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1.17</v>
       </c>
       <c r="F9" s="7">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>10.020000000000001</v>
+        <v>12.8</v>
       </c>
       <c r="H9" s="7">
         <f t="shared" si="1"/>
-        <v>80.160000000000011</v>
+        <v>102.4</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" si="2"/>
-        <v>84.378947368421066</v>
+        <v>107.78947368421053</v>
       </c>
       <c r="J9" s="7">
         <f t="shared" si="3"/>
-        <v>173.75789473684213</v>
+        <v>220.57894736842107</v>
       </c>
       <c r="K9" s="7">
-        <v>175</v>
+        <v>220</v>
       </c>
       <c r="L9" s="9">
         <f t="shared" si="4"/>
-        <v>185</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B10" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="5">
         <v>6.61</v>
       </c>
-      <c r="E10" s="10">
-        <v>1.4</v>
+      <c r="E10" s="6">
+        <v>0.93</v>
       </c>
       <c r="F10" s="7">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
       <c r="G10" s="8">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="H10" s="7">
         <f t="shared" si="1"/>
-        <v>67.2</v>
+        <v>62.4</v>
       </c>
       <c r="I10" s="7">
         <f t="shared" si="2"/>
-        <v>70.736842105263165</v>
+        <v>65.684210526315795</v>
       </c>
       <c r="J10" s="7">
         <f t="shared" si="3"/>
-        <v>146.47368421052633</v>
+        <v>136.36842105263159</v>
       </c>
       <c r="K10" s="7">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="L10" s="9">
         <f t="shared" si="4"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3">
+        <v>30</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="5">
+        <v>8.23</v>
+      </c>
+      <c r="E11" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0.39</v>
+      </c>
+      <c r="G11" s="8">
+        <f t="shared" si="0"/>
+        <v>10.020000000000001</v>
+      </c>
+      <c r="H11" s="7">
+        <f t="shared" si="1"/>
+        <v>80.160000000000011</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="2"/>
+        <v>84.378947368421066</v>
+      </c>
+      <c r="J11" s="7">
+        <f t="shared" si="3"/>
+        <v>173.75789473684213</v>
+      </c>
+      <c r="K11" s="7">
+        <v>175</v>
+      </c>
+      <c r="L11" s="9">
+        <f t="shared" si="4"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>1</v>
+      </c>
+      <c r="B12" s="3">
+        <v>30</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="5">
+        <v>6.61</v>
+      </c>
+      <c r="E12" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="F12" s="7">
+        <v>0.39</v>
+      </c>
+      <c r="G12" s="8">
+        <f t="shared" si="0"/>
+        <v>8.4</v>
+      </c>
+      <c r="H12" s="7">
+        <f t="shared" si="1"/>
+        <v>67.2</v>
+      </c>
+      <c r="I12" s="7">
+        <f t="shared" si="2"/>
+        <v>70.736842105263165</v>
+      </c>
+      <c r="J12" s="7">
+        <f t="shared" si="3"/>
+        <v>146.47368421052633</v>
+      </c>
+      <c r="K12" s="7">
+        <v>150</v>
+      </c>
+      <c r="L12" s="9">
+        <f t="shared" si="4"/>
         <v>160</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1815,25 +1945,29 @@
     <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:L10">
-    <sortCondition descending="1" ref="A5:A10"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:L12">
+    <sortCondition descending="1" ref="A7:A12"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D10" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{158232D1-5A33-4F23-96FE-CBBD1062997F}"/>
-    <hyperlink ref="D9" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E4E5833E-4068-4B7C-B15B-8751DDC64332}"/>
-    <hyperlink ref="D8" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{617E7749-47A4-47BF-9B49-B7021524E0CD}"/>
-    <hyperlink ref="D7" r:id="rId4" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{373D7045-F276-4CA0-92CD-7DDFEEF88D44}"/>
-    <hyperlink ref="D6" r:id="rId5" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{72EFFD19-DCEF-424B-99B5-9CD2ABDFC16A}"/>
-    <hyperlink ref="D5" r:id="rId6" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{2BAC9E25-EE87-4D34-BF2C-E18DBF9252D5}"/>
+    <hyperlink ref="D12" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{158232D1-5A33-4F23-96FE-CBBD1062997F}"/>
+    <hyperlink ref="D11" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E4E5833E-4068-4B7C-B15B-8751DDC64332}"/>
+    <hyperlink ref="D10" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{617E7749-47A4-47BF-9B49-B7021524E0CD}"/>
+    <hyperlink ref="D9" r:id="rId4" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{373D7045-F276-4CA0-92CD-7DDFEEF88D44}"/>
+    <hyperlink ref="D8" r:id="rId5" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{72EFFD19-DCEF-424B-99B5-9CD2ABDFC16A}"/>
+    <hyperlink ref="D7" r:id="rId6" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{2BAC9E25-EE87-4D34-BF2C-E18DBF9252D5}"/>
     <hyperlink ref="D4" r:id="rId7" display="https://detail.1688.com/offer/1002175660973.html" xr:uid="{8B5C1529-184D-4C9D-8502-E6BCED7B68FF}"/>
+    <hyperlink ref="D6" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{CF81DDA2-BDC3-4A00-959A-69CA6BFFD70C}"/>
+    <hyperlink ref="D5" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B293EB1B-C9EA-440F-B4C3-3474E10057AA}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId8"/>
-  <drawing r:id="rId9"/>
+  <pageSetup orientation="portrait" r:id="rId10"/>
+  <drawing r:id="rId11"/>
 </worksheet>
 </file>
--- a/PULSERAS SWA.xlsx
+++ b/PULSERAS SWA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8EB13E-470E-43C6-8F48-48A7073723B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3692C8-4C8E-4363-A4CE-4C64DA58D524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC752115-4679-4725-9595-0BAF90178FFC}"/>
   </bookViews>
@@ -319,13 +319,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>295275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1362075</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>981075</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -362,13 +362,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>295275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1343025</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>1028700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -405,13 +405,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1343025</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>1009650</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -448,13 +448,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>333375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1304925</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>1057275</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -491,13 +491,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>323850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>904875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -534,13 +534,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>361950</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1295400</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>923925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -621,13 +621,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>247650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1323975</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>993337</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -665,13 +665,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1266825</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>984667</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -697,6 +697,138 @@
         <a:xfrm>
           <a:off x="1571625" y="2171700"/>
           <a:ext cx="1171575" cy="756067"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>171451</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1276350</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1028817</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagen 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B924A03E-C07D-CF49-9F9E-3EF6B9D9F6E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1524000" y="2114551"/>
+          <a:ext cx="1228725" cy="857366"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>123826</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1285875</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>999596</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Imagen 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10074FA3-0A1A-64D5-8535-C5EFB180FB5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1533525" y="2066926"/>
+          <a:ext cx="1228725" cy="875770"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>257174</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1263650</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>933449</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Imagen 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{447EAA92-7A8F-EBAC-404D-CF8F2855E1FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1562100" y="2200274"/>
+          <a:ext cx="1177925" cy="676275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1028,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D45025-46D8-4DF0-A314-E30E9C4D1102}">
-  <dimension ref="A2:L550"/>
+  <dimension ref="A2:L553"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1121,14 +1253,14 @@
     </row>
     <row r="5" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5" s="3">
         <v>15</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="11">
-        <v>6.68</v>
+        <v>4.16</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="7"/>
@@ -1138,19 +1270,19 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="9">
-        <v>165</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3">
         <v>15</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="11">
-        <v>7.43</v>
+        <v>4.75</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="7"/>
@@ -1160,258 +1292,321 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="9">
-        <v>180</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3">
         <v>15</v>
       </c>
       <c r="C7" s="4"/>
-      <c r="D7" s="5">
-        <v>5.14</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F7" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G7" s="8">
-        <f t="shared" ref="G7:G12" si="0">D7+E7+F7</f>
-        <v>6.03</v>
-      </c>
-      <c r="H7" s="7">
-        <f t="shared" ref="H7:H12" si="1">G7*8</f>
-        <v>48.24</v>
-      </c>
-      <c r="I7" s="7">
-        <f t="shared" ref="I7:I12" si="2">H7/0.95</f>
-        <v>50.778947368421058</v>
-      </c>
-      <c r="J7" s="7">
-        <f t="shared" ref="J7:J12" si="3">(I7*2)+5</f>
-        <v>106.55789473684212</v>
-      </c>
-      <c r="K7" s="7">
-        <v>110</v>
-      </c>
+      <c r="D7" s="11">
+        <v>4.01</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
       <c r="L7" s="9">
-        <f t="shared" ref="L7:L12" si="4">K7+10</f>
         <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B8" s="3">
         <v>15</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="5">
-        <v>5.29</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F8" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G8" s="8">
-        <f t="shared" si="0"/>
-        <v>6.1800000000000006</v>
-      </c>
-      <c r="H8" s="7">
-        <f t="shared" si="1"/>
-        <v>49.440000000000005</v>
-      </c>
-      <c r="I8" s="7">
-        <f t="shared" si="2"/>
-        <v>52.0421052631579</v>
-      </c>
-      <c r="J8" s="7">
-        <f t="shared" si="3"/>
-        <v>109.0842105263158</v>
-      </c>
-      <c r="K8" s="7">
-        <v>110</v>
-      </c>
+      <c r="D8" s="11">
+        <v>6.68</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
       <c r="L8" s="9">
-        <f t="shared" si="4"/>
-        <v>120</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="5">
-        <v>11.31</v>
-      </c>
-      <c r="E9" s="6">
-        <v>1.17</v>
-      </c>
-      <c r="F9" s="7">
-        <v>0.32</v>
-      </c>
-      <c r="G9" s="8">
-        <f t="shared" si="0"/>
-        <v>12.8</v>
-      </c>
-      <c r="H9" s="7">
-        <f t="shared" si="1"/>
-        <v>102.4</v>
-      </c>
-      <c r="I9" s="7">
-        <f t="shared" si="2"/>
-        <v>107.78947368421053</v>
-      </c>
-      <c r="J9" s="7">
-        <f t="shared" si="3"/>
-        <v>220.57894736842107</v>
-      </c>
-      <c r="K9" s="7">
-        <v>220</v>
-      </c>
+      <c r="D9" s="11">
+        <v>7.43</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
       <c r="L9" s="9">
-        <f t="shared" si="4"/>
-        <v>230</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B10" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="5">
-        <v>6.61</v>
+        <v>5.14</v>
       </c>
       <c r="E10" s="6">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="F10" s="7">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="G10" s="8">
-        <f t="shared" si="0"/>
-        <v>7.8</v>
+        <f t="shared" ref="G10:G15" si="0">D10+E10+F10</f>
+        <v>6.03</v>
       </c>
       <c r="H10" s="7">
-        <f t="shared" si="1"/>
-        <v>62.4</v>
+        <f t="shared" ref="H10:H15" si="1">G10*8</f>
+        <v>48.24</v>
       </c>
       <c r="I10" s="7">
-        <f t="shared" si="2"/>
-        <v>65.684210526315795</v>
+        <f t="shared" ref="I10:I15" si="2">H10/0.95</f>
+        <v>50.778947368421058</v>
       </c>
       <c r="J10" s="7">
-        <f t="shared" si="3"/>
-        <v>136.36842105263159</v>
+        <f t="shared" ref="J10:J15" si="3">(I10*2)+5</f>
+        <v>106.55789473684212</v>
       </c>
       <c r="K10" s="7">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="L10" s="9">
-        <f t="shared" si="4"/>
-        <v>150</v>
+        <f t="shared" ref="L10:L15" si="4">K10+10</f>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B11" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="5">
-        <v>8.23</v>
-      </c>
-      <c r="E11" s="10">
-        <v>1.4</v>
+        <v>5.29</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.7</v>
       </c>
       <c r="F11" s="7">
-        <v>0.39</v>
+        <v>0.19</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>10.020000000000001</v>
+        <v>6.1800000000000006</v>
       </c>
       <c r="H11" s="7">
         <f t="shared" si="1"/>
-        <v>80.160000000000011</v>
+        <v>49.440000000000005</v>
       </c>
       <c r="I11" s="7">
         <f t="shared" si="2"/>
-        <v>84.378947368421066</v>
+        <v>52.0421052631579</v>
       </c>
       <c r="J11" s="7">
         <f t="shared" si="3"/>
-        <v>173.75789473684213</v>
+        <v>109.0842105263158</v>
       </c>
       <c r="K11" s="7">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="L11" s="9">
         <f t="shared" si="4"/>
-        <v>185</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B12" s="3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="5">
-        <v>6.61</v>
-      </c>
-      <c r="E12" s="10">
-        <v>1.4</v>
+        <v>11.31</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1.17</v>
       </c>
       <c r="F12" s="7">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="G12" s="8">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>12.8</v>
       </c>
       <c r="H12" s="7">
         <f t="shared" si="1"/>
-        <v>67.2</v>
+        <v>102.4</v>
       </c>
       <c r="I12" s="7">
         <f t="shared" si="2"/>
-        <v>70.736842105263165</v>
+        <v>107.78947368421053</v>
       </c>
       <c r="J12" s="7">
         <f t="shared" si="3"/>
-        <v>146.47368421052633</v>
+        <v>220.57894736842107</v>
       </c>
       <c r="K12" s="7">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="L12" s="9">
         <f t="shared" si="4"/>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>3</v>
+      </c>
+      <c r="B13" s="3">
+        <v>20</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="5">
+        <v>6.61</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="F13" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="G13" s="8">
+        <f t="shared" si="0"/>
+        <v>7.8</v>
+      </c>
+      <c r="H13" s="7">
+        <f t="shared" si="1"/>
+        <v>62.4</v>
+      </c>
+      <c r="I13" s="7">
+        <f t="shared" si="2"/>
+        <v>65.684210526315795</v>
+      </c>
+      <c r="J13" s="7">
+        <f t="shared" si="3"/>
+        <v>136.36842105263159</v>
+      </c>
+      <c r="K13" s="7">
+        <v>140</v>
+      </c>
+      <c r="L13" s="9">
+        <f t="shared" si="4"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>2</v>
+      </c>
+      <c r="B14" s="3">
+        <v>30</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="5">
+        <v>8.23</v>
+      </c>
+      <c r="E14" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="F14" s="7">
+        <v>0.39</v>
+      </c>
+      <c r="G14" s="8">
+        <f t="shared" si="0"/>
+        <v>10.020000000000001</v>
+      </c>
+      <c r="H14" s="7">
+        <f t="shared" si="1"/>
+        <v>80.160000000000011</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" si="2"/>
+        <v>84.378947368421066</v>
+      </c>
+      <c r="J14" s="7">
+        <f t="shared" si="3"/>
+        <v>173.75789473684213</v>
+      </c>
+      <c r="K14" s="7">
+        <v>175</v>
+      </c>
+      <c r="L14" s="9">
+        <f t="shared" si="4"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>1</v>
+      </c>
+      <c r="B15" s="3">
+        <v>30</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5">
+        <v>6.61</v>
+      </c>
+      <c r="E15" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="F15" s="7">
+        <v>0.39</v>
+      </c>
+      <c r="G15" s="8">
+        <f t="shared" si="0"/>
+        <v>8.4</v>
+      </c>
+      <c r="H15" s="7">
+        <f t="shared" si="1"/>
+        <v>67.2</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" si="2"/>
+        <v>70.736842105263165</v>
+      </c>
+      <c r="J15" s="7">
+        <f t="shared" si="3"/>
+        <v>146.47368421052633</v>
+      </c>
+      <c r="K15" s="7">
+        <v>150</v>
+      </c>
+      <c r="L15" s="9">
+        <f t="shared" si="4"/>
         <v>160</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1947,27 +2142,33 @@
     <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:L12">
-    <sortCondition descending="1" ref="A7:A12"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:L15">
+    <sortCondition descending="1" ref="A10:A15"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D12" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{158232D1-5A33-4F23-96FE-CBBD1062997F}"/>
-    <hyperlink ref="D11" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E4E5833E-4068-4B7C-B15B-8751DDC64332}"/>
-    <hyperlink ref="D10" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{617E7749-47A4-47BF-9B49-B7021524E0CD}"/>
-    <hyperlink ref="D9" r:id="rId4" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{373D7045-F276-4CA0-92CD-7DDFEEF88D44}"/>
-    <hyperlink ref="D8" r:id="rId5" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{72EFFD19-DCEF-424B-99B5-9CD2ABDFC16A}"/>
-    <hyperlink ref="D7" r:id="rId6" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{2BAC9E25-EE87-4D34-BF2C-E18DBF9252D5}"/>
+    <hyperlink ref="D15" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{158232D1-5A33-4F23-96FE-CBBD1062997F}"/>
+    <hyperlink ref="D14" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E4E5833E-4068-4B7C-B15B-8751DDC64332}"/>
+    <hyperlink ref="D13" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{617E7749-47A4-47BF-9B49-B7021524E0CD}"/>
+    <hyperlink ref="D12" r:id="rId4" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{373D7045-F276-4CA0-92CD-7DDFEEF88D44}"/>
+    <hyperlink ref="D11" r:id="rId5" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{72EFFD19-DCEF-424B-99B5-9CD2ABDFC16A}"/>
+    <hyperlink ref="D10" r:id="rId6" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{2BAC9E25-EE87-4D34-BF2C-E18DBF9252D5}"/>
     <hyperlink ref="D4" r:id="rId7" display="https://detail.1688.com/offer/1002175660973.html" xr:uid="{8B5C1529-184D-4C9D-8502-E6BCED7B68FF}"/>
-    <hyperlink ref="D6" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{CF81DDA2-BDC3-4A00-959A-69CA6BFFD70C}"/>
-    <hyperlink ref="D5" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B293EB1B-C9EA-440F-B4C3-3474E10057AA}"/>
+    <hyperlink ref="D9" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{CF81DDA2-BDC3-4A00-959A-69CA6BFFD70C}"/>
+    <hyperlink ref="D8" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B293EB1B-C9EA-440F-B4C3-3474E10057AA}"/>
+    <hyperlink ref="D7" r:id="rId10" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{DE499952-02A4-4C2C-8E63-8F21101C392A}"/>
+    <hyperlink ref="D6" r:id="rId11" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{2DF1EA40-2501-4812-A33B-F9751BA90050}"/>
+    <hyperlink ref="D5" r:id="rId12" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{C012995A-0862-436E-AB44-66474FCA20F8}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId10"/>
-  <drawing r:id="rId11"/>
+  <pageSetup orientation="portrait" r:id="rId13"/>
+  <drawing r:id="rId14"/>
 </worksheet>
 </file>
--- a/PULSERAS SWA.xlsx
+++ b/PULSERAS SWA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3692C8-4C8E-4363-A4CE-4C64DA58D524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34AA1FFA-74D7-49AF-839B-2D187679451F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC752115-4679-4725-9595-0BAF90178FFC}"/>
   </bookViews>
@@ -319,13 +319,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>295275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1362075</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>981075</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -362,13 +362,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>295275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1343025</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>1028700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -405,13 +405,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1343025</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>1009650</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -448,13 +448,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>333375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1304925</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>1057275</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -491,13 +491,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>323850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>904875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -534,13 +534,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>361950</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1295400</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>923925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -621,13 +621,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>247650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1323975</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>993337</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -665,13 +665,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1266825</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>984667</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -709,13 +709,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>171451</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1276350</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>1028817</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -753,13 +753,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>123826</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1285875</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>999596</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -797,13 +797,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>257174</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1263650</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>933449</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -829,6 +829,226 @@
         <a:xfrm>
           <a:off x="1562100" y="2200274"/>
           <a:ext cx="1177925" cy="676275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>66676</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>295275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1337650</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1009650</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Imagen 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69133F20-75A2-F89E-89E6-54D7E39A6620}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1543051" y="2238375"/>
+          <a:ext cx="1270974" cy="714375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>199782</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1266825</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1201142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Imagen 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{722648D5-6FC9-F0DA-75D6-D8CCABEEEA2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1552575" y="2142882"/>
+          <a:ext cx="1190625" cy="1001360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1326784</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1028700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Imagen 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32F8724A-5FCD-216A-42EA-12E9BC2285E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1543050" y="2162175"/>
+          <a:ext cx="1260109" cy="809625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>114301</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>131087</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1190625</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1111289</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Imagen 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99D63723-24CD-077D-D52B-83AD37863B9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1590676" y="2074187"/>
+          <a:ext cx="1076324" cy="980202"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>238125</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1338455</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>914400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Imagen 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CD86526-F5B8-A163-FD52-27A6C17C1786}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1543050" y="2181225"/>
+          <a:ext cx="1271780" cy="676275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1160,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D45025-46D8-4DF0-A314-E30E9C4D1102}">
-  <dimension ref="A2:L553"/>
+  <dimension ref="A2:L558"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1253,14 +1473,14 @@
     </row>
     <row r="5" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="11">
-        <v>4.16</v>
+        <v>7.43</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="7"/>
@@ -1270,19 +1490,19 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="9">
-        <v>120</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B6" s="3">
         <v>15</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="11">
-        <v>4.75</v>
+        <v>7.43</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="7"/>
@@ -1292,19 +1512,19 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="9">
-        <v>130</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B7" s="3">
         <v>15</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="11">
-        <v>4.01</v>
+        <v>6.68</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
@@ -1314,19 +1534,19 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="9">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B8" s="3">
         <v>15</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="11">
-        <v>6.68</v>
+        <v>7.43</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="7"/>
@@ -1336,19 +1556,19 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="9">
-        <v>165</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B9" s="3">
         <v>15</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="11">
-        <v>7.43</v>
+        <v>5.49</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="7"/>
@@ -1358,272 +1578,377 @@
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="9">
-        <v>180</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B10" s="3">
         <v>15</v>
       </c>
       <c r="C10" s="4"/>
-      <c r="D10" s="5">
-        <v>5.14</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F10" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G10" s="8">
-        <f t="shared" ref="G10:G15" si="0">D10+E10+F10</f>
-        <v>6.03</v>
-      </c>
-      <c r="H10" s="7">
-        <f t="shared" ref="H10:H15" si="1">G10*8</f>
-        <v>48.24</v>
-      </c>
-      <c r="I10" s="7">
-        <f t="shared" ref="I10:I15" si="2">H10/0.95</f>
-        <v>50.778947368421058</v>
-      </c>
-      <c r="J10" s="7">
-        <f t="shared" ref="J10:J15" si="3">(I10*2)+5</f>
-        <v>106.55789473684212</v>
-      </c>
-      <c r="K10" s="7">
-        <v>110</v>
-      </c>
+      <c r="D10" s="11">
+        <v>4.16</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
       <c r="L10" s="9">
-        <f t="shared" ref="L10:L15" si="4">K10+10</f>
-        <v>120</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
         <v>15</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="5">
-        <v>5.29</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F11" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G11" s="8">
-        <f t="shared" si="0"/>
-        <v>6.1800000000000006</v>
-      </c>
-      <c r="H11" s="7">
-        <f t="shared" si="1"/>
-        <v>49.440000000000005</v>
-      </c>
-      <c r="I11" s="7">
-        <f t="shared" si="2"/>
-        <v>52.0421052631579</v>
-      </c>
-      <c r="J11" s="7">
-        <f t="shared" si="3"/>
-        <v>109.0842105263158</v>
-      </c>
-      <c r="K11" s="7">
-        <v>110</v>
-      </c>
+      <c r="D11" s="11">
+        <v>4.75</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
       <c r="L11" s="9">
-        <f t="shared" si="4"/>
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B12" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="5">
-        <v>11.31</v>
-      </c>
-      <c r="E12" s="6">
-        <v>1.17</v>
-      </c>
-      <c r="F12" s="7">
-        <v>0.32</v>
-      </c>
-      <c r="G12" s="8">
-        <f t="shared" si="0"/>
-        <v>12.8</v>
-      </c>
-      <c r="H12" s="7">
-        <f t="shared" si="1"/>
-        <v>102.4</v>
-      </c>
-      <c r="I12" s="7">
-        <f t="shared" si="2"/>
-        <v>107.78947368421053</v>
-      </c>
-      <c r="J12" s="7">
-        <f t="shared" si="3"/>
-        <v>220.57894736842107</v>
-      </c>
-      <c r="K12" s="7">
-        <v>220</v>
-      </c>
+      <c r="D12" s="11">
+        <v>4.01</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
       <c r="L12" s="9">
-        <f t="shared" si="4"/>
-        <v>230</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B13" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" s="4"/>
-      <c r="D13" s="5">
-        <v>6.61</v>
-      </c>
-      <c r="E13" s="6">
-        <v>0.93</v>
-      </c>
-      <c r="F13" s="7">
-        <v>0.26</v>
-      </c>
-      <c r="G13" s="8">
-        <f t="shared" si="0"/>
-        <v>7.8</v>
-      </c>
-      <c r="H13" s="7">
-        <f t="shared" si="1"/>
-        <v>62.4</v>
-      </c>
-      <c r="I13" s="7">
-        <f t="shared" si="2"/>
-        <v>65.684210526315795</v>
-      </c>
-      <c r="J13" s="7">
-        <f t="shared" si="3"/>
-        <v>136.36842105263159</v>
-      </c>
-      <c r="K13" s="7">
-        <v>140</v>
-      </c>
+      <c r="D13" s="11">
+        <v>6.68</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
       <c r="L13" s="9">
-        <f t="shared" si="4"/>
-        <v>150</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B14" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="5">
-        <v>8.23</v>
-      </c>
-      <c r="E14" s="10">
-        <v>1.4</v>
-      </c>
-      <c r="F14" s="7">
-        <v>0.39</v>
-      </c>
-      <c r="G14" s="8">
-        <f t="shared" si="0"/>
-        <v>10.020000000000001</v>
-      </c>
-      <c r="H14" s="7">
-        <f t="shared" si="1"/>
-        <v>80.160000000000011</v>
-      </c>
-      <c r="I14" s="7">
-        <f t="shared" si="2"/>
-        <v>84.378947368421066</v>
-      </c>
-      <c r="J14" s="7">
-        <f t="shared" si="3"/>
-        <v>173.75789473684213</v>
-      </c>
-      <c r="K14" s="7">
-        <v>175</v>
-      </c>
+      <c r="D14" s="11">
+        <v>7.43</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
       <c r="L14" s="9">
-        <f t="shared" si="4"/>
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B15" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="5">
+        <v>5.14</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F15" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G15" s="8">
+        <f t="shared" ref="G15:G20" si="0">D15+E15+F15</f>
+        <v>6.03</v>
+      </c>
+      <c r="H15" s="7">
+        <f t="shared" ref="H15:H20" si="1">G15*8</f>
+        <v>48.24</v>
+      </c>
+      <c r="I15" s="7">
+        <f t="shared" ref="I15:I20" si="2">H15/0.95</f>
+        <v>50.778947368421058</v>
+      </c>
+      <c r="J15" s="7">
+        <f t="shared" ref="J15:J20" si="3">(I15*2)+5</f>
+        <v>106.55789473684212</v>
+      </c>
+      <c r="K15" s="7">
+        <v>110</v>
+      </c>
+      <c r="L15" s="9">
+        <f t="shared" ref="L15:L20" si="4">K15+10</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>5</v>
+      </c>
+      <c r="B16" s="3">
+        <v>15</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="5">
+        <v>5.29</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="F16" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="G16" s="8">
+        <f t="shared" si="0"/>
+        <v>6.1800000000000006</v>
+      </c>
+      <c r="H16" s="7">
+        <f t="shared" si="1"/>
+        <v>49.440000000000005</v>
+      </c>
+      <c r="I16" s="7">
+        <f t="shared" si="2"/>
+        <v>52.0421052631579</v>
+      </c>
+      <c r="J16" s="7">
+        <f t="shared" si="3"/>
+        <v>109.0842105263158</v>
+      </c>
+      <c r="K16" s="7">
+        <v>110</v>
+      </c>
+      <c r="L16" s="9">
+        <f t="shared" si="4"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>4</v>
+      </c>
+      <c r="B17" s="3">
+        <v>25</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5">
+        <v>11.31</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.17</v>
+      </c>
+      <c r="F17" s="7">
+        <v>0.32</v>
+      </c>
+      <c r="G17" s="8">
+        <f t="shared" si="0"/>
+        <v>12.8</v>
+      </c>
+      <c r="H17" s="7">
+        <f t="shared" si="1"/>
+        <v>102.4</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="2"/>
+        <v>107.78947368421053</v>
+      </c>
+      <c r="J17" s="7">
+        <f t="shared" si="3"/>
+        <v>220.57894736842107</v>
+      </c>
+      <c r="K17" s="7">
+        <v>220</v>
+      </c>
+      <c r="L17" s="9">
+        <f t="shared" si="4"/>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>3</v>
+      </c>
+      <c r="B18" s="3">
+        <v>20</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="5">
         <v>6.61</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E18" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="F18" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="G18" s="8">
+        <f t="shared" si="0"/>
+        <v>7.8</v>
+      </c>
+      <c r="H18" s="7">
+        <f t="shared" si="1"/>
+        <v>62.4</v>
+      </c>
+      <c r="I18" s="7">
+        <f t="shared" si="2"/>
+        <v>65.684210526315795</v>
+      </c>
+      <c r="J18" s="7">
+        <f t="shared" si="3"/>
+        <v>136.36842105263159</v>
+      </c>
+      <c r="K18" s="7">
+        <v>140</v>
+      </c>
+      <c r="L18" s="9">
+        <f t="shared" si="4"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>2</v>
+      </c>
+      <c r="B19" s="3">
+        <v>30</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="5">
+        <v>8.23</v>
+      </c>
+      <c r="E19" s="10">
         <v>1.4</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F19" s="7">
         <v>0.39</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G19" s="8">
+        <f t="shared" si="0"/>
+        <v>10.020000000000001</v>
+      </c>
+      <c r="H19" s="7">
+        <f t="shared" si="1"/>
+        <v>80.160000000000011</v>
+      </c>
+      <c r="I19" s="7">
+        <f t="shared" si="2"/>
+        <v>84.378947368421066</v>
+      </c>
+      <c r="J19" s="7">
+        <f t="shared" si="3"/>
+        <v>173.75789473684213</v>
+      </c>
+      <c r="K19" s="7">
+        <v>175</v>
+      </c>
+      <c r="L19" s="9">
+        <f t="shared" si="4"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>1</v>
+      </c>
+      <c r="B20" s="3">
+        <v>30</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="5">
+        <v>6.61</v>
+      </c>
+      <c r="E20" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="F20" s="7">
+        <v>0.39</v>
+      </c>
+      <c r="G20" s="8">
         <f t="shared" si="0"/>
         <v>8.4</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H20" s="7">
         <f t="shared" si="1"/>
         <v>67.2</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I20" s="7">
         <f t="shared" si="2"/>
         <v>70.736842105263165</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J20" s="7">
         <f t="shared" si="3"/>
         <v>146.47368421052633</v>
       </c>
-      <c r="K15" s="7">
+      <c r="K20" s="7">
         <v>150</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L20" s="9">
         <f t="shared" si="4"/>
         <v>160</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2145,30 +2470,40 @@
     <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:L15">
-    <sortCondition descending="1" ref="A10:A15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A15:L20">
+    <sortCondition descending="1" ref="A15:A20"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D15" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{158232D1-5A33-4F23-96FE-CBBD1062997F}"/>
-    <hyperlink ref="D14" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E4E5833E-4068-4B7C-B15B-8751DDC64332}"/>
-    <hyperlink ref="D13" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{617E7749-47A4-47BF-9B49-B7021524E0CD}"/>
-    <hyperlink ref="D12" r:id="rId4" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{373D7045-F276-4CA0-92CD-7DDFEEF88D44}"/>
-    <hyperlink ref="D11" r:id="rId5" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{72EFFD19-DCEF-424B-99B5-9CD2ABDFC16A}"/>
-    <hyperlink ref="D10" r:id="rId6" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{2BAC9E25-EE87-4D34-BF2C-E18DBF9252D5}"/>
+    <hyperlink ref="D20" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{158232D1-5A33-4F23-96FE-CBBD1062997F}"/>
+    <hyperlink ref="D19" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E4E5833E-4068-4B7C-B15B-8751DDC64332}"/>
+    <hyperlink ref="D18" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{617E7749-47A4-47BF-9B49-B7021524E0CD}"/>
+    <hyperlink ref="D17" r:id="rId4" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{373D7045-F276-4CA0-92CD-7DDFEEF88D44}"/>
+    <hyperlink ref="D16" r:id="rId5" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{72EFFD19-DCEF-424B-99B5-9CD2ABDFC16A}"/>
+    <hyperlink ref="D15" r:id="rId6" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{2BAC9E25-EE87-4D34-BF2C-E18DBF9252D5}"/>
     <hyperlink ref="D4" r:id="rId7" display="https://detail.1688.com/offer/1002175660973.html" xr:uid="{8B5C1529-184D-4C9D-8502-E6BCED7B68FF}"/>
-    <hyperlink ref="D9" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{CF81DDA2-BDC3-4A00-959A-69CA6BFFD70C}"/>
-    <hyperlink ref="D8" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B293EB1B-C9EA-440F-B4C3-3474E10057AA}"/>
-    <hyperlink ref="D7" r:id="rId10" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{DE499952-02A4-4C2C-8E63-8F21101C392A}"/>
-    <hyperlink ref="D6" r:id="rId11" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{2DF1EA40-2501-4812-A33B-F9751BA90050}"/>
-    <hyperlink ref="D5" r:id="rId12" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{C012995A-0862-436E-AB44-66474FCA20F8}"/>
+    <hyperlink ref="D14" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{CF81DDA2-BDC3-4A00-959A-69CA6BFFD70C}"/>
+    <hyperlink ref="D13" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B293EB1B-C9EA-440F-B4C3-3474E10057AA}"/>
+    <hyperlink ref="D12" r:id="rId10" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{DE499952-02A4-4C2C-8E63-8F21101C392A}"/>
+    <hyperlink ref="D11" r:id="rId11" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{2DF1EA40-2501-4812-A33B-F9751BA90050}"/>
+    <hyperlink ref="D10" r:id="rId12" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{C012995A-0862-436E-AB44-66474FCA20F8}"/>
+    <hyperlink ref="D9" r:id="rId13" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{A3634CCC-D2BD-47BB-9187-AE7B5CD519AC}"/>
+    <hyperlink ref="D8" r:id="rId14" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{E2E63D84-F39E-4819-925E-BC1CB4A4583B}"/>
+    <hyperlink ref="D7" r:id="rId15" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{3F7B0CAE-4D84-4244-B520-51B623C25D83}"/>
+    <hyperlink ref="D6" r:id="rId16" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{0A0478BA-1EC0-4894-ACC2-58E767F176E2}"/>
+    <hyperlink ref="D5" r:id="rId17" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{61A8C19F-25F0-4C1B-A51D-054E33AB2B16}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId13"/>
-  <drawing r:id="rId14"/>
+  <pageSetup orientation="portrait" r:id="rId18"/>
+  <drawing r:id="rId19"/>
 </worksheet>
 </file>
--- a/PULSERAS SWA.xlsx
+++ b/PULSERAS SWA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34AA1FFA-74D7-49AF-839B-2D187679451F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C31C796-6DC7-465E-8AAB-F80D89A06653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC752115-4679-4725-9595-0BAF90178FFC}"/>
   </bookViews>
@@ -319,14 +319,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>295275</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1362075</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>981075</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1114425</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -347,8 +347,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1571625" y="971550"/>
-          <a:ext cx="1266825" cy="685800"/>
+          <a:off x="1571625" y="21078825"/>
+          <a:ext cx="1266825" cy="981075"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -361,15 +361,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>295275</xdr:rowOff>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1343025</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>1028700</xdr:rowOff>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1171574</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -390,8 +390,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1552575" y="2238375"/>
-          <a:ext cx="1266825" cy="733425"/>
+          <a:off x="1562100" y="19764375"/>
+          <a:ext cx="1266825" cy="1085849"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -405,14 +405,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1343025</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>1009650</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1209675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -433,8 +433,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1581150" y="3438525"/>
-          <a:ext cx="1238250" cy="781050"/>
+          <a:off x="1581150" y="18478500"/>
+          <a:ext cx="1238250" cy="1143000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -448,14 +448,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>333375</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1304925</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>1057275</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1209675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -476,8 +476,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1552575" y="4810125"/>
-          <a:ext cx="1228725" cy="723900"/>
+          <a:off x="1552575" y="17306925"/>
+          <a:ext cx="1228725" cy="1047750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -491,14 +491,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>323850</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>904875</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1114424</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -519,8 +519,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1571625" y="6067425"/>
-          <a:ext cx="1219200" cy="581025"/>
+          <a:off x="1571625" y="16002000"/>
+          <a:ext cx="1219200" cy="990599"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -534,14 +534,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>361950</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1295400</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>923925</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1143000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -562,8 +562,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1552575" y="7372350"/>
-          <a:ext cx="1219200" cy="561975"/>
+          <a:off x="1552575" y="14716125"/>
+          <a:ext cx="1219200" cy="1038225"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -621,13 +621,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>247650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1323975</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>993337</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -665,13 +665,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1266825</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>984667</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -709,13 +709,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>171451</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1276350</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>1028817</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -753,13 +753,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>123826</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1285875</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>999596</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -797,13 +797,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>257174</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1263650</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>933449</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -841,13 +841,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>66676</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>295275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1337650</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>1009650</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -885,13 +885,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>199782</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1266825</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>1201142</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -929,13 +929,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1326784</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>1028700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -973,13 +973,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>114301</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>131087</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1190625</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>1111289</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1017,13 +1017,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>238125</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1338455</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>914400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1049,6 +1049,50 @@
         <a:xfrm>
           <a:off x="1543050" y="2181225"/>
           <a:ext cx="1271780" cy="676275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>76201</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1352551</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1172458</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Imagen 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{182617B2-5065-19DA-4296-135D34640786}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1552576" y="2057400"/>
+          <a:ext cx="1276350" cy="1058158"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1380,7 +1424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D45025-46D8-4DF0-A314-E30E9C4D1102}">
-  <dimension ref="A2:L558"/>
+  <dimension ref="A2:L559"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1473,14 +1517,14 @@
     </row>
     <row r="5" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="11">
-        <v>7.43</v>
+        <v>8.61</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="7"/>
@@ -1490,15 +1534,15 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="9">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="11">
@@ -1512,19 +1556,19 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="9">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="3">
         <v>15</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="11">
-        <v>6.68</v>
+        <v>7.43</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
@@ -1539,14 +1583,14 @@
     </row>
     <row r="8" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="3">
         <v>15</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="11">
-        <v>7.43</v>
+        <v>6.68</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="7"/>
@@ -1561,14 +1605,14 @@
     </row>
     <row r="9" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="3">
         <v>15</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="11">
-        <v>5.49</v>
+        <v>7.43</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="7"/>
@@ -1578,19 +1622,19 @@
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="9">
-        <v>145</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="3">
         <v>15</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="11">
-        <v>4.16</v>
+        <v>5.49</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="7"/>
@@ -1605,14 +1649,14 @@
     </row>
     <row r="11" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3">
         <v>15</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="11">
-        <v>4.75</v>
+        <v>4.16</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="7"/>
@@ -1622,19 +1666,19 @@
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="9">
-        <v>130</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="3">
         <v>15</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="11">
-        <v>4.01</v>
+        <v>4.75</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
@@ -1644,19 +1688,19 @@
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="9">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" s="3">
         <v>15</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="11">
-        <v>6.68</v>
+        <v>4.01</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
@@ -1666,19 +1710,19 @@
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="9">
-        <v>165</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B14" s="3">
         <v>15</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="11">
-        <v>7.43</v>
+        <v>6.68</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="7"/>
@@ -1688,60 +1732,41 @@
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="9">
-        <v>180</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B15" s="3">
         <v>15</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="5">
-        <v>5.14</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F15" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G15" s="8">
-        <f t="shared" ref="G15:G20" si="0">D15+E15+F15</f>
-        <v>6.03</v>
-      </c>
-      <c r="H15" s="7">
-        <f t="shared" ref="H15:H20" si="1">G15*8</f>
-        <v>48.24</v>
-      </c>
-      <c r="I15" s="7">
-        <f t="shared" ref="I15:I20" si="2">H15/0.95</f>
-        <v>50.778947368421058</v>
-      </c>
-      <c r="J15" s="7">
-        <f t="shared" ref="J15:J20" si="3">(I15*2)+5</f>
-        <v>106.55789473684212</v>
-      </c>
-      <c r="K15" s="7">
-        <v>110</v>
-      </c>
+      <c r="D15" s="11">
+        <v>7.43</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
       <c r="L15" s="9">
-        <f t="shared" ref="L15:L20" si="4">K15+10</f>
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B16" s="3">
         <v>15</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="5">
-        <v>5.29</v>
+        <v>5.14</v>
       </c>
       <c r="E16" s="6">
         <v>0.7</v>
@@ -1750,162 +1775,162 @@
         <v>0.19</v>
       </c>
       <c r="G16" s="8">
-        <f t="shared" si="0"/>
-        <v>6.1800000000000006</v>
+        <f t="shared" ref="G16:G21" si="0">D16+E16+F16</f>
+        <v>6.03</v>
       </c>
       <c r="H16" s="7">
-        <f t="shared" si="1"/>
-        <v>49.440000000000005</v>
+        <f t="shared" ref="H16:H21" si="1">G16*8</f>
+        <v>48.24</v>
       </c>
       <c r="I16" s="7">
-        <f t="shared" si="2"/>
-        <v>52.0421052631579</v>
+        <f t="shared" ref="I16:I21" si="2">H16/0.95</f>
+        <v>50.778947368421058</v>
       </c>
       <c r="J16" s="7">
-        <f t="shared" si="3"/>
-        <v>109.0842105263158</v>
+        <f t="shared" ref="J16:J21" si="3">(I16*2)+5</f>
+        <v>106.55789473684212</v>
       </c>
       <c r="K16" s="7">
         <v>110</v>
       </c>
       <c r="L16" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="L16:L21" si="4">K16+10</f>
         <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B17" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="5">
-        <v>11.31</v>
+        <v>5.29</v>
       </c>
       <c r="E17" s="6">
-        <v>1.17</v>
+        <v>0.7</v>
       </c>
       <c r="F17" s="7">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>12.8</v>
+        <v>6.1800000000000006</v>
       </c>
       <c r="H17" s="7">
         <f t="shared" si="1"/>
-        <v>102.4</v>
+        <v>49.440000000000005</v>
       </c>
       <c r="I17" s="7">
         <f t="shared" si="2"/>
-        <v>107.78947368421053</v>
+        <v>52.0421052631579</v>
       </c>
       <c r="J17" s="7">
         <f t="shared" si="3"/>
-        <v>220.57894736842107</v>
+        <v>109.0842105263158</v>
       </c>
       <c r="K17" s="7">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="L17" s="9">
         <f t="shared" si="4"/>
-        <v>230</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="5">
-        <v>6.61</v>
+        <v>11.31</v>
       </c>
       <c r="E18" s="6">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
       <c r="F18" s="7">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="G18" s="8">
         <f t="shared" si="0"/>
-        <v>7.8</v>
+        <v>12.8</v>
       </c>
       <c r="H18" s="7">
         <f t="shared" si="1"/>
-        <v>62.4</v>
+        <v>102.4</v>
       </c>
       <c r="I18" s="7">
         <f t="shared" si="2"/>
-        <v>65.684210526315795</v>
+        <v>107.78947368421053</v>
       </c>
       <c r="J18" s="7">
         <f t="shared" si="3"/>
-        <v>136.36842105263159</v>
+        <v>220.57894736842107</v>
       </c>
       <c r="K18" s="7">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="L18" s="9">
         <f t="shared" si="4"/>
-        <v>150</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="5">
-        <v>8.23</v>
-      </c>
-      <c r="E19" s="10">
-        <v>1.4</v>
+        <v>6.61</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.93</v>
       </c>
       <c r="F19" s="7">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>10.020000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="H19" s="7">
         <f t="shared" si="1"/>
-        <v>80.160000000000011</v>
+        <v>62.4</v>
       </c>
       <c r="I19" s="7">
         <f t="shared" si="2"/>
-        <v>84.378947368421066</v>
+        <v>65.684210526315795</v>
       </c>
       <c r="J19" s="7">
         <f t="shared" si="3"/>
-        <v>173.75789473684213</v>
+        <v>136.36842105263159</v>
       </c>
       <c r="K19" s="7">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="L19" s="9">
         <f t="shared" si="4"/>
-        <v>185</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" s="3">
         <v>30</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="5">
-        <v>6.61</v>
+        <v>8.23</v>
       </c>
       <c r="E20" s="10">
         <v>1.4</v>
@@ -1915,29 +1940,69 @@
       </c>
       <c r="G20" s="8">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>10.020000000000001</v>
       </c>
       <c r="H20" s="7">
         <f t="shared" si="1"/>
-        <v>67.2</v>
+        <v>80.160000000000011</v>
       </c>
       <c r="I20" s="7">
         <f t="shared" si="2"/>
-        <v>70.736842105263165</v>
+        <v>84.378947368421066</v>
       </c>
       <c r="J20" s="7">
         <f t="shared" si="3"/>
-        <v>146.47368421052633</v>
+        <v>173.75789473684213</v>
       </c>
       <c r="K20" s="7">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="L20" s="9">
         <f t="shared" si="4"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>1</v>
+      </c>
+      <c r="B21" s="3">
+        <v>30</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5">
+        <v>6.61</v>
+      </c>
+      <c r="E21" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="F21" s="7">
+        <v>0.39</v>
+      </c>
+      <c r="G21" s="8">
+        <f t="shared" si="0"/>
+        <v>8.4</v>
+      </c>
+      <c r="H21" s="7">
+        <f t="shared" si="1"/>
+        <v>67.2</v>
+      </c>
+      <c r="I21" s="7">
+        <f t="shared" si="2"/>
+        <v>70.736842105263165</v>
+      </c>
+      <c r="J21" s="7">
+        <f t="shared" si="3"/>
+        <v>146.47368421052633</v>
+      </c>
+      <c r="K21" s="7">
+        <v>150</v>
+      </c>
+      <c r="L21" s="9">
+        <f t="shared" si="4"/>
         <v>160</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2475,35 +2540,37 @@
     <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A15:L20">
-    <sortCondition descending="1" ref="A15:A20"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:L21">
+    <sortCondition descending="1" ref="A16:A21"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D20" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{158232D1-5A33-4F23-96FE-CBBD1062997F}"/>
-    <hyperlink ref="D19" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E4E5833E-4068-4B7C-B15B-8751DDC64332}"/>
-    <hyperlink ref="D18" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{617E7749-47A4-47BF-9B49-B7021524E0CD}"/>
-    <hyperlink ref="D17" r:id="rId4" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{373D7045-F276-4CA0-92CD-7DDFEEF88D44}"/>
-    <hyperlink ref="D16" r:id="rId5" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{72EFFD19-DCEF-424B-99B5-9CD2ABDFC16A}"/>
-    <hyperlink ref="D15" r:id="rId6" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{2BAC9E25-EE87-4D34-BF2C-E18DBF9252D5}"/>
+    <hyperlink ref="D21" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{158232D1-5A33-4F23-96FE-CBBD1062997F}"/>
+    <hyperlink ref="D20" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E4E5833E-4068-4B7C-B15B-8751DDC64332}"/>
+    <hyperlink ref="D19" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{617E7749-47A4-47BF-9B49-B7021524E0CD}"/>
+    <hyperlink ref="D18" r:id="rId4" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{373D7045-F276-4CA0-92CD-7DDFEEF88D44}"/>
+    <hyperlink ref="D17" r:id="rId5" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{72EFFD19-DCEF-424B-99B5-9CD2ABDFC16A}"/>
+    <hyperlink ref="D16" r:id="rId6" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{2BAC9E25-EE87-4D34-BF2C-E18DBF9252D5}"/>
     <hyperlink ref="D4" r:id="rId7" display="https://detail.1688.com/offer/1002175660973.html" xr:uid="{8B5C1529-184D-4C9D-8502-E6BCED7B68FF}"/>
-    <hyperlink ref="D14" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{CF81DDA2-BDC3-4A00-959A-69CA6BFFD70C}"/>
-    <hyperlink ref="D13" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B293EB1B-C9EA-440F-B4C3-3474E10057AA}"/>
-    <hyperlink ref="D12" r:id="rId10" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{DE499952-02A4-4C2C-8E63-8F21101C392A}"/>
-    <hyperlink ref="D11" r:id="rId11" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{2DF1EA40-2501-4812-A33B-F9751BA90050}"/>
-    <hyperlink ref="D10" r:id="rId12" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{C012995A-0862-436E-AB44-66474FCA20F8}"/>
-    <hyperlink ref="D9" r:id="rId13" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{A3634CCC-D2BD-47BB-9187-AE7B5CD519AC}"/>
-    <hyperlink ref="D8" r:id="rId14" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{E2E63D84-F39E-4819-925E-BC1CB4A4583B}"/>
-    <hyperlink ref="D7" r:id="rId15" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{3F7B0CAE-4D84-4244-B520-51B623C25D83}"/>
-    <hyperlink ref="D6" r:id="rId16" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{0A0478BA-1EC0-4894-ACC2-58E767F176E2}"/>
-    <hyperlink ref="D5" r:id="rId17" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{61A8C19F-25F0-4C1B-A51D-054E33AB2B16}"/>
+    <hyperlink ref="D15" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{CF81DDA2-BDC3-4A00-959A-69CA6BFFD70C}"/>
+    <hyperlink ref="D14" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B293EB1B-C9EA-440F-B4C3-3474E10057AA}"/>
+    <hyperlink ref="D13" r:id="rId10" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{DE499952-02A4-4C2C-8E63-8F21101C392A}"/>
+    <hyperlink ref="D12" r:id="rId11" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{2DF1EA40-2501-4812-A33B-F9751BA90050}"/>
+    <hyperlink ref="D11" r:id="rId12" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{C012995A-0862-436E-AB44-66474FCA20F8}"/>
+    <hyperlink ref="D10" r:id="rId13" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{A3634CCC-D2BD-47BB-9187-AE7B5CD519AC}"/>
+    <hyperlink ref="D9" r:id="rId14" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{E2E63D84-F39E-4819-925E-BC1CB4A4583B}"/>
+    <hyperlink ref="D8" r:id="rId15" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{3F7B0CAE-4D84-4244-B520-51B623C25D83}"/>
+    <hyperlink ref="D7" r:id="rId16" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{0A0478BA-1EC0-4894-ACC2-58E767F176E2}"/>
+    <hyperlink ref="D6" r:id="rId17" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{61A8C19F-25F0-4C1B-A51D-054E33AB2B16}"/>
+    <hyperlink ref="D5" r:id="rId18" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{9178A1F4-3784-44D9-AA72-0D888215AEAC}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId18"/>
-  <drawing r:id="rId19"/>
+  <pageSetup orientation="portrait" r:id="rId19"/>
+  <drawing r:id="rId20"/>
 </worksheet>
 </file>
--- a/PULSERAS SWA.xlsx
+++ b/PULSERAS SWA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C31C796-6DC7-465E-8AAB-F80D89A06653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBDF7F05-57B3-48DB-A584-04D87349E45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC752115-4679-4725-9595-0BAF90178FFC}"/>
   </bookViews>
@@ -319,13 +319,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1362075</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>1114425</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -362,13 +362,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>1171574</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -405,13 +405,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1343025</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>1209675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -448,13 +448,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1304925</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>1209675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -491,13 +491,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>1114424</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -534,13 +534,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1295400</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>1143000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -621,13 +621,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>247650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1323975</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>993337</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -665,13 +665,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1266825</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>984667</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -709,13 +709,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>171451</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1276350</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>1028817</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -753,13 +753,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>123826</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1285875</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>999596</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -797,13 +797,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>257174</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1263650</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>933449</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -841,13 +841,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>66676</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>295275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1337650</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>1009650</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -885,13 +885,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>199782</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1266825</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>1201142</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -929,13 +929,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1326784</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>1028700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -973,13 +973,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>114301</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>131087</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1190625</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>1111289</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1017,13 +1017,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>238125</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1338455</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>914400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1061,13 +1061,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76201</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1352551</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>1172458</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1093,6 +1093,50 @@
         <a:xfrm>
           <a:off x="1552576" y="2057400"/>
           <a:ext cx="1276350" cy="1058158"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123826</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>104774</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1258931</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1057275</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Imagen 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F537D890-926E-5918-9AD4-BF491EB5032A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1600201" y="2047874"/>
+          <a:ext cx="1135105" cy="952501"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1424,7 +1468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D45025-46D8-4DF0-A314-E30E9C4D1102}">
-  <dimension ref="A2:L559"/>
+  <dimension ref="A2:L560"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1517,14 +1561,14 @@
     </row>
     <row r="5" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" s="3">
         <v>15</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="11">
-        <v>8.61</v>
+        <v>6.85</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="7"/>
@@ -1534,19 +1578,19 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="9">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="11">
-        <v>7.43</v>
+        <v>8.61</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="7"/>
@@ -1556,15 +1600,15 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="9">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="11">
@@ -1578,19 +1622,19 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="9">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="3">
         <v>15</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="11">
-        <v>6.68</v>
+        <v>7.43</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="7"/>
@@ -1605,14 +1649,14 @@
     </row>
     <row r="9" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="3">
         <v>15</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="11">
-        <v>7.43</v>
+        <v>6.68</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="7"/>
@@ -1627,14 +1671,14 @@
     </row>
     <row r="10" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="3">
         <v>15</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="11">
-        <v>5.49</v>
+        <v>7.43</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="7"/>
@@ -1644,19 +1688,19 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="9">
-        <v>145</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" s="3">
         <v>15</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="11">
-        <v>4.16</v>
+        <v>5.49</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="7"/>
@@ -1671,14 +1715,14 @@
     </row>
     <row r="12" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
         <v>15</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="11">
-        <v>4.75</v>
+        <v>4.16</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
@@ -1688,19 +1732,19 @@
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="9">
-        <v>130</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" s="3">
         <v>15</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="11">
-        <v>4.01</v>
+        <v>4.75</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
@@ -1710,19 +1754,19 @@
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="9">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" s="3">
         <v>15</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="11">
-        <v>6.68</v>
+        <v>4.01</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="7"/>
@@ -1732,19 +1776,19 @@
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="9">
-        <v>165</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B15" s="3">
         <v>15</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="11">
-        <v>7.43</v>
+        <v>6.68</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="7"/>
@@ -1754,60 +1798,41 @@
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="9">
-        <v>180</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B16" s="3">
         <v>15</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="5">
-        <v>5.14</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F16" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G16" s="8">
-        <f t="shared" ref="G16:G21" si="0">D16+E16+F16</f>
-        <v>6.03</v>
-      </c>
-      <c r="H16" s="7">
-        <f t="shared" ref="H16:H21" si="1">G16*8</f>
-        <v>48.24</v>
-      </c>
-      <c r="I16" s="7">
-        <f t="shared" ref="I16:I21" si="2">H16/0.95</f>
-        <v>50.778947368421058</v>
-      </c>
-      <c r="J16" s="7">
-        <f t="shared" ref="J16:J21" si="3">(I16*2)+5</f>
-        <v>106.55789473684212</v>
-      </c>
-      <c r="K16" s="7">
-        <v>110</v>
-      </c>
+      <c r="D16" s="11">
+        <v>7.43</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
       <c r="L16" s="9">
-        <f t="shared" ref="L16:L21" si="4">K16+10</f>
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B17" s="3">
         <v>15</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="5">
-        <v>5.29</v>
+        <v>5.14</v>
       </c>
       <c r="E17" s="6">
         <v>0.7</v>
@@ -1816,162 +1841,162 @@
         <v>0.19</v>
       </c>
       <c r="G17" s="8">
-        <f t="shared" si="0"/>
-        <v>6.1800000000000006</v>
+        <f t="shared" ref="G17:G22" si="0">D17+E17+F17</f>
+        <v>6.03</v>
       </c>
       <c r="H17" s="7">
-        <f t="shared" si="1"/>
-        <v>49.440000000000005</v>
+        <f t="shared" ref="H17:H22" si="1">G17*8</f>
+        <v>48.24</v>
       </c>
       <c r="I17" s="7">
-        <f t="shared" si="2"/>
-        <v>52.0421052631579</v>
+        <f t="shared" ref="I17:I22" si="2">H17/0.95</f>
+        <v>50.778947368421058</v>
       </c>
       <c r="J17" s="7">
-        <f t="shared" si="3"/>
-        <v>109.0842105263158</v>
+        <f t="shared" ref="J17:J22" si="3">(I17*2)+5</f>
+        <v>106.55789473684212</v>
       </c>
       <c r="K17" s="7">
         <v>110</v>
       </c>
       <c r="L17" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="L17:L22" si="4">K17+10</f>
         <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="5">
-        <v>11.31</v>
+        <v>5.29</v>
       </c>
       <c r="E18" s="6">
-        <v>1.17</v>
+        <v>0.7</v>
       </c>
       <c r="F18" s="7">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="G18" s="8">
         <f t="shared" si="0"/>
-        <v>12.8</v>
+        <v>6.1800000000000006</v>
       </c>
       <c r="H18" s="7">
         <f t="shared" si="1"/>
-        <v>102.4</v>
+        <v>49.440000000000005</v>
       </c>
       <c r="I18" s="7">
         <f t="shared" si="2"/>
-        <v>107.78947368421053</v>
+        <v>52.0421052631579</v>
       </c>
       <c r="J18" s="7">
         <f t="shared" si="3"/>
-        <v>220.57894736842107</v>
+        <v>109.0842105263158</v>
       </c>
       <c r="K18" s="7">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="L18" s="9">
         <f t="shared" si="4"/>
-        <v>230</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B19" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="5">
-        <v>6.61</v>
+        <v>11.31</v>
       </c>
       <c r="E19" s="6">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
       <c r="F19" s="7">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>7.8</v>
+        <v>12.8</v>
       </c>
       <c r="H19" s="7">
         <f t="shared" si="1"/>
-        <v>62.4</v>
+        <v>102.4</v>
       </c>
       <c r="I19" s="7">
         <f t="shared" si="2"/>
-        <v>65.684210526315795</v>
+        <v>107.78947368421053</v>
       </c>
       <c r="J19" s="7">
         <f t="shared" si="3"/>
-        <v>136.36842105263159</v>
+        <v>220.57894736842107</v>
       </c>
       <c r="K19" s="7">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="L19" s="9">
         <f t="shared" si="4"/>
-        <v>150</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="5">
-        <v>8.23</v>
-      </c>
-      <c r="E20" s="10">
-        <v>1.4</v>
+        <v>6.61</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.93</v>
       </c>
       <c r="F20" s="7">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
       <c r="G20" s="8">
         <f t="shared" si="0"/>
-        <v>10.020000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="H20" s="7">
         <f t="shared" si="1"/>
-        <v>80.160000000000011</v>
+        <v>62.4</v>
       </c>
       <c r="I20" s="7">
         <f t="shared" si="2"/>
-        <v>84.378947368421066</v>
+        <v>65.684210526315795</v>
       </c>
       <c r="J20" s="7">
         <f t="shared" si="3"/>
-        <v>173.75789473684213</v>
+        <v>136.36842105263159</v>
       </c>
       <c r="K20" s="7">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="L20" s="9">
         <f t="shared" si="4"/>
-        <v>185</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" s="3">
         <v>30</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="5">
-        <v>6.61</v>
+        <v>8.23</v>
       </c>
       <c r="E21" s="10">
         <v>1.4</v>
@@ -1981,29 +2006,69 @@
       </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>10.020000000000001</v>
       </c>
       <c r="H21" s="7">
         <f t="shared" si="1"/>
-        <v>67.2</v>
+        <v>80.160000000000011</v>
       </c>
       <c r="I21" s="7">
         <f t="shared" si="2"/>
-        <v>70.736842105263165</v>
+        <v>84.378947368421066</v>
       </c>
       <c r="J21" s="7">
         <f t="shared" si="3"/>
-        <v>146.47368421052633</v>
+        <v>173.75789473684213</v>
       </c>
       <c r="K21" s="7">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="L21" s="9">
         <f t="shared" si="4"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>1</v>
+      </c>
+      <c r="B22" s="3">
+        <v>30</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5">
+        <v>6.61</v>
+      </c>
+      <c r="E22" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="F22" s="7">
+        <v>0.39</v>
+      </c>
+      <c r="G22" s="8">
+        <f t="shared" si="0"/>
+        <v>8.4</v>
+      </c>
+      <c r="H22" s="7">
+        <f t="shared" si="1"/>
+        <v>67.2</v>
+      </c>
+      <c r="I22" s="7">
+        <f t="shared" si="2"/>
+        <v>70.736842105263165</v>
+      </c>
+      <c r="J22" s="7">
+        <f t="shared" si="3"/>
+        <v>146.47368421052633</v>
+      </c>
+      <c r="K22" s="7">
+        <v>150</v>
+      </c>
+      <c r="L22" s="9">
+        <f t="shared" si="4"/>
         <v>160</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2541,36 +2606,38 @@
     <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:L21">
-    <sortCondition descending="1" ref="A16:A21"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A17:L22">
+    <sortCondition descending="1" ref="A17:A22"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D21" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{158232D1-5A33-4F23-96FE-CBBD1062997F}"/>
-    <hyperlink ref="D20" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E4E5833E-4068-4B7C-B15B-8751DDC64332}"/>
-    <hyperlink ref="D19" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{617E7749-47A4-47BF-9B49-B7021524E0CD}"/>
-    <hyperlink ref="D18" r:id="rId4" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{373D7045-F276-4CA0-92CD-7DDFEEF88D44}"/>
-    <hyperlink ref="D17" r:id="rId5" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{72EFFD19-DCEF-424B-99B5-9CD2ABDFC16A}"/>
-    <hyperlink ref="D16" r:id="rId6" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{2BAC9E25-EE87-4D34-BF2C-E18DBF9252D5}"/>
+    <hyperlink ref="D22" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{158232D1-5A33-4F23-96FE-CBBD1062997F}"/>
+    <hyperlink ref="D21" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E4E5833E-4068-4B7C-B15B-8751DDC64332}"/>
+    <hyperlink ref="D20" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{617E7749-47A4-47BF-9B49-B7021524E0CD}"/>
+    <hyperlink ref="D19" r:id="rId4" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{373D7045-F276-4CA0-92CD-7DDFEEF88D44}"/>
+    <hyperlink ref="D18" r:id="rId5" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{72EFFD19-DCEF-424B-99B5-9CD2ABDFC16A}"/>
+    <hyperlink ref="D17" r:id="rId6" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{2BAC9E25-EE87-4D34-BF2C-E18DBF9252D5}"/>
     <hyperlink ref="D4" r:id="rId7" display="https://detail.1688.com/offer/1002175660973.html" xr:uid="{8B5C1529-184D-4C9D-8502-E6BCED7B68FF}"/>
-    <hyperlink ref="D15" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{CF81DDA2-BDC3-4A00-959A-69CA6BFFD70C}"/>
-    <hyperlink ref="D14" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B293EB1B-C9EA-440F-B4C3-3474E10057AA}"/>
-    <hyperlink ref="D13" r:id="rId10" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{DE499952-02A4-4C2C-8E63-8F21101C392A}"/>
-    <hyperlink ref="D12" r:id="rId11" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{2DF1EA40-2501-4812-A33B-F9751BA90050}"/>
-    <hyperlink ref="D11" r:id="rId12" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{C012995A-0862-436E-AB44-66474FCA20F8}"/>
-    <hyperlink ref="D10" r:id="rId13" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{A3634CCC-D2BD-47BB-9187-AE7B5CD519AC}"/>
-    <hyperlink ref="D9" r:id="rId14" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{E2E63D84-F39E-4819-925E-BC1CB4A4583B}"/>
-    <hyperlink ref="D8" r:id="rId15" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{3F7B0CAE-4D84-4244-B520-51B623C25D83}"/>
-    <hyperlink ref="D7" r:id="rId16" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{0A0478BA-1EC0-4894-ACC2-58E767F176E2}"/>
-    <hyperlink ref="D6" r:id="rId17" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{61A8C19F-25F0-4C1B-A51D-054E33AB2B16}"/>
-    <hyperlink ref="D5" r:id="rId18" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{9178A1F4-3784-44D9-AA72-0D888215AEAC}"/>
+    <hyperlink ref="D16" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{CF81DDA2-BDC3-4A00-959A-69CA6BFFD70C}"/>
+    <hyperlink ref="D15" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B293EB1B-C9EA-440F-B4C3-3474E10057AA}"/>
+    <hyperlink ref="D14" r:id="rId10" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{DE499952-02A4-4C2C-8E63-8F21101C392A}"/>
+    <hyperlink ref="D13" r:id="rId11" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{2DF1EA40-2501-4812-A33B-F9751BA90050}"/>
+    <hyperlink ref="D12" r:id="rId12" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{C012995A-0862-436E-AB44-66474FCA20F8}"/>
+    <hyperlink ref="D11" r:id="rId13" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{A3634CCC-D2BD-47BB-9187-AE7B5CD519AC}"/>
+    <hyperlink ref="D10" r:id="rId14" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{E2E63D84-F39E-4819-925E-BC1CB4A4583B}"/>
+    <hyperlink ref="D9" r:id="rId15" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{3F7B0CAE-4D84-4244-B520-51B623C25D83}"/>
+    <hyperlink ref="D8" r:id="rId16" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{0A0478BA-1EC0-4894-ACC2-58E767F176E2}"/>
+    <hyperlink ref="D7" r:id="rId17" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{61A8C19F-25F0-4C1B-A51D-054E33AB2B16}"/>
+    <hyperlink ref="D6" r:id="rId18" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{9178A1F4-3784-44D9-AA72-0D888215AEAC}"/>
+    <hyperlink ref="D5" r:id="rId19" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{1D9B82F1-1D03-4BD1-A208-BE5840189C29}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId19"/>
-  <drawing r:id="rId20"/>
+  <pageSetup orientation="portrait" r:id="rId20"/>
+  <drawing r:id="rId21"/>
 </worksheet>
 </file>
--- a/PULSERAS SWA.xlsx
+++ b/PULSERAS SWA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBDF7F05-57B3-48DB-A584-04D87349E45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034FAF66-5735-438C-B31B-D62E40196D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC752115-4679-4725-9595-0BAF90178FFC}"/>
   </bookViews>
@@ -319,13 +319,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1362075</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>1114425</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -362,13 +362,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>1171574</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -405,13 +405,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1343025</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>1209675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -448,13 +448,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1304925</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>1209675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -491,13 +491,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1314450</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>1114424</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -534,13 +534,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1295400</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>1143000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -621,13 +621,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>247650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1323975</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>993337</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -665,13 +665,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1266825</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>984667</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -709,13 +709,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>171451</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1276350</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>1028817</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -753,13 +753,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>123826</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1285875</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>999596</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -797,13 +797,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>257174</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1263650</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>933449</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -841,13 +841,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>66676</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>295275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1337650</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>1009650</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -885,13 +885,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>199782</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1266825</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>1201142</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -929,13 +929,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1326784</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>1028700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -973,13 +973,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>114301</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>131087</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1190625</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>1111289</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1017,13 +1017,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>238125</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1338455</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>914400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1061,13 +1061,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>76201</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1352551</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>1172458</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1105,13 +1105,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123826</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>104774</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1258931</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>1057275</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1137,6 +1137,50 @@
         <a:xfrm>
           <a:off x="1600201" y="2047874"/>
           <a:ext cx="1135105" cy="952501"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>333375</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1285875</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>792368</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Imagen 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9602AEA-E783-1537-8E65-8239CD069B9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1543050" y="2276475"/>
+          <a:ext cx="1219200" cy="458993"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1468,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37D45025-46D8-4DF0-A314-E30E9C4D1102}">
-  <dimension ref="A2:L560"/>
+  <dimension ref="A2:L561"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1561,14 +1605,14 @@
     </row>
     <row r="5" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="3">
         <v>15</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="11">
-        <v>6.85</v>
+        <v>5.95</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="7"/>
@@ -1578,19 +1622,19 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="9">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="3">
         <v>15</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="11">
-        <v>8.61</v>
+        <v>6.85</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="7"/>
@@ -1600,19 +1644,19 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="9">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="11">
-        <v>7.43</v>
+        <v>8.61</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
@@ -1622,15 +1666,15 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="9">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="11">
@@ -1644,19 +1688,19 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="9">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="3">
         <v>15</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="11">
-        <v>6.68</v>
+        <v>7.43</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="7"/>
@@ -1671,14 +1715,14 @@
     </row>
     <row r="10" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="3">
         <v>15</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="11">
-        <v>7.43</v>
+        <v>6.68</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="7"/>
@@ -1693,14 +1737,14 @@
     </row>
     <row r="11" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="3">
         <v>15</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="11">
-        <v>5.49</v>
+        <v>7.43</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="7"/>
@@ -1710,19 +1754,19 @@
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="9">
-        <v>145</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="3">
         <v>15</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="11">
-        <v>4.16</v>
+        <v>5.49</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
@@ -1737,14 +1781,14 @@
     </row>
     <row r="13" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3">
         <v>15</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="11">
-        <v>4.75</v>
+        <v>4.16</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
@@ -1754,19 +1798,19 @@
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="9">
-        <v>130</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B14" s="3">
         <v>15</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="11">
-        <v>4.01</v>
+        <v>4.75</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="7"/>
@@ -1776,19 +1820,19 @@
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="9">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" s="3">
         <v>15</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="11">
-        <v>6.68</v>
+        <v>4.01</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="7"/>
@@ -1798,19 +1842,19 @@
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="9">
-        <v>165</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B16" s="3">
         <v>15</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="11">
-        <v>7.43</v>
+        <v>6.68</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="7"/>
@@ -1820,60 +1864,41 @@
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
       <c r="L16" s="9">
-        <v>180</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B17" s="3">
         <v>15</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="D17" s="5">
-        <v>5.14</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="F17" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="G17" s="8">
-        <f t="shared" ref="G17:G22" si="0">D17+E17+F17</f>
-        <v>6.03</v>
-      </c>
-      <c r="H17" s="7">
-        <f t="shared" ref="H17:H22" si="1">G17*8</f>
-        <v>48.24</v>
-      </c>
-      <c r="I17" s="7">
-        <f t="shared" ref="I17:I22" si="2">H17/0.95</f>
-        <v>50.778947368421058</v>
-      </c>
-      <c r="J17" s="7">
-        <f t="shared" ref="J17:J22" si="3">(I17*2)+5</f>
-        <v>106.55789473684212</v>
-      </c>
-      <c r="K17" s="7">
-        <v>110</v>
-      </c>
+      <c r="D17" s="11">
+        <v>7.43</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
       <c r="L17" s="9">
-        <f t="shared" ref="L17:L22" si="4">K17+10</f>
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B18" s="3">
         <v>15</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="5">
-        <v>5.29</v>
+        <v>5.14</v>
       </c>
       <c r="E18" s="6">
         <v>0.7</v>
@@ -1882,162 +1907,162 @@
         <v>0.19</v>
       </c>
       <c r="G18" s="8">
-        <f t="shared" si="0"/>
-        <v>6.1800000000000006</v>
+        <f t="shared" ref="G18:G23" si="0">D18+E18+F18</f>
+        <v>6.03</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="1"/>
-        <v>49.440000000000005</v>
+        <f t="shared" ref="H18:H23" si="1">G18*8</f>
+        <v>48.24</v>
       </c>
       <c r="I18" s="7">
-        <f t="shared" si="2"/>
-        <v>52.0421052631579</v>
+        <f t="shared" ref="I18:I23" si="2">H18/0.95</f>
+        <v>50.778947368421058</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" si="3"/>
-        <v>109.0842105263158</v>
+        <f t="shared" ref="J18:J23" si="3">(I18*2)+5</f>
+        <v>106.55789473684212</v>
       </c>
       <c r="K18" s="7">
         <v>110</v>
       </c>
       <c r="L18" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="L18:L23" si="4">K18+10</f>
         <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B19" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="5">
-        <v>11.31</v>
+        <v>5.29</v>
       </c>
       <c r="E19" s="6">
-        <v>1.17</v>
+        <v>0.7</v>
       </c>
       <c r="F19" s="7">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>12.8</v>
+        <v>6.1800000000000006</v>
       </c>
       <c r="H19" s="7">
         <f t="shared" si="1"/>
-        <v>102.4</v>
+        <v>49.440000000000005</v>
       </c>
       <c r="I19" s="7">
         <f t="shared" si="2"/>
-        <v>107.78947368421053</v>
+        <v>52.0421052631579</v>
       </c>
       <c r="J19" s="7">
         <f t="shared" si="3"/>
-        <v>220.57894736842107</v>
+        <v>109.0842105263158</v>
       </c>
       <c r="K19" s="7">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="L19" s="9">
         <f t="shared" si="4"/>
-        <v>230</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B20" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="5">
-        <v>6.61</v>
+        <v>11.31</v>
       </c>
       <c r="E20" s="6">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
       <c r="F20" s="7">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="G20" s="8">
         <f t="shared" si="0"/>
-        <v>7.8</v>
+        <v>12.8</v>
       </c>
       <c r="H20" s="7">
         <f t="shared" si="1"/>
-        <v>62.4</v>
+        <v>102.4</v>
       </c>
       <c r="I20" s="7">
         <f t="shared" si="2"/>
-        <v>65.684210526315795</v>
+        <v>107.78947368421053</v>
       </c>
       <c r="J20" s="7">
         <f t="shared" si="3"/>
-        <v>136.36842105263159</v>
+        <v>220.57894736842107</v>
       </c>
       <c r="K20" s="7">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="L20" s="9">
         <f t="shared" si="4"/>
-        <v>150</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="5">
-        <v>8.23</v>
-      </c>
-      <c r="E21" s="10">
-        <v>1.4</v>
+        <v>6.61</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.93</v>
       </c>
       <c r="F21" s="7">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
-        <v>10.020000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="H21" s="7">
         <f t="shared" si="1"/>
-        <v>80.160000000000011</v>
+        <v>62.4</v>
       </c>
       <c r="I21" s="7">
         <f t="shared" si="2"/>
-        <v>84.378947368421066</v>
+        <v>65.684210526315795</v>
       </c>
       <c r="J21" s="7">
         <f t="shared" si="3"/>
-        <v>173.75789473684213</v>
+        <v>136.36842105263159</v>
       </c>
       <c r="K21" s="7">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="L21" s="9">
         <f t="shared" si="4"/>
-        <v>185</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" s="3">
         <v>30</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="5">
-        <v>6.61</v>
+        <v>8.23</v>
       </c>
       <c r="E22" s="10">
         <v>1.4</v>
@@ -2047,29 +2072,69 @@
       </c>
       <c r="G22" s="8">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>10.020000000000001</v>
       </c>
       <c r="H22" s="7">
         <f t="shared" si="1"/>
-        <v>67.2</v>
+        <v>80.160000000000011</v>
       </c>
       <c r="I22" s="7">
         <f t="shared" si="2"/>
-        <v>70.736842105263165</v>
+        <v>84.378947368421066</v>
       </c>
       <c r="J22" s="7">
         <f t="shared" si="3"/>
-        <v>146.47368421052633</v>
+        <v>173.75789473684213</v>
       </c>
       <c r="K22" s="7">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="L22" s="9">
         <f t="shared" si="4"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>1</v>
+      </c>
+      <c r="B23" s="3">
+        <v>30</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="5">
+        <v>6.61</v>
+      </c>
+      <c r="E23" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="F23" s="7">
+        <v>0.39</v>
+      </c>
+      <c r="G23" s="8">
+        <f t="shared" si="0"/>
+        <v>8.4</v>
+      </c>
+      <c r="H23" s="7">
+        <f t="shared" si="1"/>
+        <v>67.2</v>
+      </c>
+      <c r="I23" s="7">
+        <f t="shared" si="2"/>
+        <v>70.736842105263165</v>
+      </c>
+      <c r="J23" s="7">
+        <f t="shared" si="3"/>
+        <v>146.47368421052633</v>
+      </c>
+      <c r="K23" s="7">
+        <v>150</v>
+      </c>
+      <c r="L23" s="9">
+        <f t="shared" si="4"/>
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2607,37 +2672,39 @@
     <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A17:L22">
-    <sortCondition descending="1" ref="A17:A22"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A18:L23">
+    <sortCondition descending="1" ref="A18:A23"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D22" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{158232D1-5A33-4F23-96FE-CBBD1062997F}"/>
-    <hyperlink ref="D21" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E4E5833E-4068-4B7C-B15B-8751DDC64332}"/>
-    <hyperlink ref="D20" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{617E7749-47A4-47BF-9B49-B7021524E0CD}"/>
-    <hyperlink ref="D19" r:id="rId4" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{373D7045-F276-4CA0-92CD-7DDFEEF88D44}"/>
-    <hyperlink ref="D18" r:id="rId5" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{72EFFD19-DCEF-424B-99B5-9CD2ABDFC16A}"/>
-    <hyperlink ref="D17" r:id="rId6" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{2BAC9E25-EE87-4D34-BF2C-E18DBF9252D5}"/>
+    <hyperlink ref="D23" r:id="rId1" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{158232D1-5A33-4F23-96FE-CBBD1062997F}"/>
+    <hyperlink ref="D22" r:id="rId2" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{E4E5833E-4068-4B7C-B15B-8751DDC64332}"/>
+    <hyperlink ref="D21" r:id="rId3" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{617E7749-47A4-47BF-9B49-B7021524E0CD}"/>
+    <hyperlink ref="D20" r:id="rId4" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{373D7045-F276-4CA0-92CD-7DDFEEF88D44}"/>
+    <hyperlink ref="D19" r:id="rId5" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{72EFFD19-DCEF-424B-99B5-9CD2ABDFC16A}"/>
+    <hyperlink ref="D18" r:id="rId6" display="https://www.sugargoo.com/products?productLink=https%253A%252F%252Fdetail.1688.com%252Foffer%252F1002132577551.html%253FkjSource%253Dpc" xr:uid="{2BAC9E25-EE87-4D34-BF2C-E18DBF9252D5}"/>
     <hyperlink ref="D4" r:id="rId7" display="https://detail.1688.com/offer/1002175660973.html" xr:uid="{8B5C1529-184D-4C9D-8502-E6BCED7B68FF}"/>
-    <hyperlink ref="D16" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{CF81DDA2-BDC3-4A00-959A-69CA6BFFD70C}"/>
-    <hyperlink ref="D15" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B293EB1B-C9EA-440F-B4C3-3474E10057AA}"/>
-    <hyperlink ref="D14" r:id="rId10" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{DE499952-02A4-4C2C-8E63-8F21101C392A}"/>
-    <hyperlink ref="D13" r:id="rId11" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{2DF1EA40-2501-4812-A33B-F9751BA90050}"/>
-    <hyperlink ref="D12" r:id="rId12" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{C012995A-0862-436E-AB44-66474FCA20F8}"/>
-    <hyperlink ref="D11" r:id="rId13" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{A3634CCC-D2BD-47BB-9187-AE7B5CD519AC}"/>
-    <hyperlink ref="D10" r:id="rId14" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{E2E63D84-F39E-4819-925E-BC1CB4A4583B}"/>
-    <hyperlink ref="D9" r:id="rId15" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{3F7B0CAE-4D84-4244-B520-51B623C25D83}"/>
-    <hyperlink ref="D8" r:id="rId16" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{0A0478BA-1EC0-4894-ACC2-58E767F176E2}"/>
-    <hyperlink ref="D7" r:id="rId17" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{61A8C19F-25F0-4C1B-A51D-054E33AB2B16}"/>
-    <hyperlink ref="D6" r:id="rId18" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{9178A1F4-3784-44D9-AA72-0D888215AEAC}"/>
-    <hyperlink ref="D5" r:id="rId19" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{1D9B82F1-1D03-4BD1-A208-BE5840189C29}"/>
+    <hyperlink ref="D17" r:id="rId8" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{CF81DDA2-BDC3-4A00-959A-69CA6BFFD70C}"/>
+    <hyperlink ref="D16" r:id="rId9" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{B293EB1B-C9EA-440F-B4C3-3474E10057AA}"/>
+    <hyperlink ref="D15" r:id="rId10" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{DE499952-02A4-4C2C-8E63-8F21101C392A}"/>
+    <hyperlink ref="D14" r:id="rId11" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{2DF1EA40-2501-4812-A33B-F9751BA90050}"/>
+    <hyperlink ref="D13" r:id="rId12" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{C012995A-0862-436E-AB44-66474FCA20F8}"/>
+    <hyperlink ref="D12" r:id="rId13" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{A3634CCC-D2BD-47BB-9187-AE7B5CD519AC}"/>
+    <hyperlink ref="D11" r:id="rId14" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{E2E63D84-F39E-4819-925E-BC1CB4A4583B}"/>
+    <hyperlink ref="D10" r:id="rId15" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{3F7B0CAE-4D84-4244-B520-51B623C25D83}"/>
+    <hyperlink ref="D9" r:id="rId16" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{0A0478BA-1EC0-4894-ACC2-58E767F176E2}"/>
+    <hyperlink ref="D8" r:id="rId17" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{61A8C19F-25F0-4C1B-A51D-054E33AB2B16}"/>
+    <hyperlink ref="D7" r:id="rId18" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{9178A1F4-3784-44D9-AA72-0D888215AEAC}"/>
+    <hyperlink ref="D6" r:id="rId19" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{1D9B82F1-1D03-4BD1-A208-BE5840189C29}"/>
+    <hyperlink ref="D5" r:id="rId20" display="https://detail.1688.com/offer/1002610604367.html" xr:uid="{7F157C59-D5B7-4B58-90AB-E6FC3256609B}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId20"/>
-  <drawing r:id="rId21"/>
+  <pageSetup orientation="portrait" r:id="rId21"/>
+  <drawing r:id="rId22"/>
 </worksheet>
 </file>